--- a/00-course-info/218-course-schedule.xlsx
+++ b/00-course-info/218-course-schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cpslo-my.sharepoint.com/personal/erobin17_calpoly_edu/Documents/stat218-calpoly/00-course-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9A7FBAEB-6D6B-4833-BA8B-814B21B863F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A902B8C7-141C-4900-B720-3D7DFC6D6F00}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{9A7FBAEB-6D6B-4833-BA8B-814B21B863F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B5811A-0C59-4D80-8C0A-B842B1DCA27A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
   <si>
     <t>Topic</t>
   </si>
@@ -90,9 +90,6 @@
     <t>Lab 2: EDA</t>
   </si>
   <si>
-    <t>???</t>
-  </si>
-  <si>
     <t>Lab 3: Inference for a single mean</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>Read ch. 1 &amp; 2 for class Wednesday</t>
   </si>
   <si>
-    <t>Midterm project part I</t>
-  </si>
-  <si>
     <t>Diving Penguins</t>
   </si>
   <si>
@@ -129,9 +123,6 @@
     <t>Sleepness nights (part II)</t>
   </si>
   <si>
-    <t>Midterm project part II</t>
-  </si>
-  <si>
     <t>Lab 4: Golf driving distance</t>
   </si>
   <si>
@@ -144,12 +135,6 @@
     <t>Group / R portion</t>
   </si>
   <si>
-    <t>EDA (IMBD revisited)</t>
-  </si>
-  <si>
-    <t>Inference (snowfall)</t>
-  </si>
-  <si>
     <t>Individual closed notes portion</t>
   </si>
   <si>
@@ -159,18 +144,9 @@
     <t>Read 20.2 + 20.3 + chapter 21 for next week</t>
   </si>
   <si>
-    <t>Confidence interval for snowfall…</t>
-  </si>
-  <si>
-    <t>Paired - covid 19 &amp; air pollution</t>
-  </si>
-  <si>
     <t>Lab 6: Color Interference</t>
   </si>
   <si>
-    <t>Return Exams</t>
-  </si>
-  <si>
     <t>Read 14.1 + 22 for Monday</t>
   </si>
   <si>
@@ -213,9 +189,6 @@
     <t>Inference for two means (paired)</t>
   </si>
   <si>
-    <t>Final Exam</t>
-  </si>
-  <si>
     <t>Read chapter 18 for next week</t>
   </si>
   <si>
@@ -229,6 +202,49 @@
   </si>
   <si>
     <t>Group Final Exam</t>
+  </si>
+  <si>
+    <t>Inference + Confidence Interval (snowfall)</t>
+  </si>
+  <si>
+    <t>Extend to Paired?</t>
+  </si>
+  <si>
+    <t>Midterm project part I: Find dataset</t>
+  </si>
+  <si>
+    <t>Midterm project part II: Create R Project</t>
+  </si>
+  <si>
+    <t>Midterm project part III: Data description + Histograms</t>
+  </si>
+  <si>
+    <t>Midterm project part IV: Scatterplot + SLR</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Return Exams / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Final Midterm Project: Interpretation</t>
+    </r>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Individual final exam</t>
+  </si>
+  <si>
+    <t>EDA two means + simulate randomization</t>
   </si>
 </sst>
 </file>
@@ -269,7 +285,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,6 +295,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -340,6 +362,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,7 +650,7 @@
     <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.6640625" customWidth="1"/>
     <col min="5" max="5" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" customWidth="1"/>
     <col min="7" max="7" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
   </cols>
@@ -652,7 +675,7 @@
         <v>7</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>5</v>
@@ -678,10 +701,10 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -700,8 +723,8 @@
       <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>15</v>
@@ -743,11 +766,11 @@
       <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
+      <c r="F5" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -764,10 +787,10 @@
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -784,13 +807,13 @@
         <v>17</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -804,13 +827,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -824,16 +847,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -847,13 +870,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -867,16 +890,16 @@
         <v>5</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="G11" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -890,13 +913,13 @@
         <v>6</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="24" t="s">
         <v>60</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -910,16 +933,16 @@
         <v>6</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -933,16 +956,16 @@
         <v>7</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -956,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -976,13 +999,13 @@
         <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -996,16 +1019,16 @@
         <v>8</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1019,13 +1042,13 @@
         <v>9</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1039,10 +1062,10 @@
         <v>9</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.3">
@@ -1084,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1098,21 +1121,21 @@
         <v>10</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21">
-        <v>44900</v>
+        <v>44898</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E24" s="23"/>
     </row>

--- a/00-course-info/218-course-schedule.xlsx
+++ b/00-course-info/218-course-schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cpslo-my.sharepoint.com/personal/erobin17_calpoly_edu/Documents/stat218-calpoly/00-course-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{9A7FBAEB-6D6B-4833-BA8B-814B21B863F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B5811A-0C59-4D80-8C0A-B842B1DCA27A}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{9A7FBAEB-6D6B-4833-BA8B-814B21B863F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{574E89D4-C30A-475B-995A-41CE1E628A48}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -165,9 +165,6 @@
     <t>Inference for one proportion</t>
   </si>
   <si>
-    <t>Lab 7: EDA</t>
-  </si>
-  <si>
     <t>Final project part I</t>
   </si>
   <si>
@@ -245,6 +242,9 @@
   </si>
   <si>
     <t>EDA two means + simulate randomization</t>
+  </si>
+  <si>
+    <t>Lab 7: Categorical EDA</t>
   </si>
 </sst>
 </file>
@@ -724,7 +724,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>15</v>
@@ -767,7 +767,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>25</v>
@@ -810,7 +810,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
@@ -853,7 +853,7 @@
         <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>37</v>
@@ -870,13 +870,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -913,13 +913,13 @@
         <v>6</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -933,13 +933,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>40</v>
@@ -979,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1002,10 +1002,10 @@
         <v>45</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="19" t="s">
         <v>49</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1028,7 +1028,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1042,13 +1042,13 @@
         <v>9</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1062,10 +1062,10 @@
         <v>9</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.3">
@@ -1107,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1121,7 +1121,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -1129,13 +1129,13 @@
         <v>44898</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" s="23"/>
     </row>
